--- a/examples/sales.xlsx
+++ b/examples/sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teoch\Documents\Personal\Github\approx\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D6128BEF-526F-4C01-B2A0-D6E0469D02ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A8BAAF-695B-4412-B994-3B3A014A6D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{FC993B36-9E35-4FE9-803B-9F990ACAC480}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
   <si>
     <t>NRIC</t>
   </si>
@@ -78,6 +78,108 @@
   </si>
   <si>
     <t>Sales</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Blk 88 Punggol St 12</t>
+  </si>
+  <si>
+    <t>Blk 20A Sengkang Ave 3</t>
+  </si>
+  <si>
+    <t>Blk 77 Simei Ave 5</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Diploma</t>
+  </si>
+  <si>
+    <t>Masters</t>
+  </si>
+  <si>
+    <t>Bachelors</t>
+  </si>
+  <si>
+    <t>S0939879D</t>
+  </si>
+  <si>
+    <t>Anton Ong</t>
+  </si>
+  <si>
+    <t>9 Mandarin Drive</t>
+  </si>
+  <si>
+    <t>Doctorate</t>
+  </si>
+  <si>
+    <t>Sales Assistant</t>
+  </si>
+  <si>
+    <t>Jr Sales Assistant</t>
+  </si>
+  <si>
+    <t>Sales Associate</t>
+  </si>
+  <si>
+    <t>Sales Director</t>
+  </si>
+  <si>
+    <t>Compensation</t>
+  </si>
+  <si>
+    <t>Promotion Percentage</t>
+  </si>
+  <si>
+    <t>S0931239E</t>
+  </si>
+  <si>
+    <t>S1234679F</t>
+  </si>
+  <si>
+    <t>S0689781B</t>
+  </si>
+  <si>
+    <t>S0931279B</t>
+  </si>
+  <si>
+    <t>S0875989E</t>
+  </si>
+  <si>
+    <t>Jasmin Li</t>
+  </si>
+  <si>
+    <t>Ravid Ashwarnan</t>
+  </si>
+  <si>
+    <t>Gombak Teo</t>
+  </si>
+  <si>
+    <t>Jalen Wong</t>
+  </si>
+  <si>
+    <t>Matthew Lee</t>
+  </si>
+  <si>
+    <t>Blk 19 Bugis St 2</t>
+  </si>
+  <si>
+    <t>Blk 88 Geylang Ln 4</t>
+  </si>
+  <si>
+    <t>Blk 22 Tampines Ave 4</t>
+  </si>
+  <si>
+    <t>Blk 10 Choa Chu Kang St 43</t>
+  </si>
+  <si>
+    <t>2 Orchard Rd</t>
   </si>
 </sst>
 </file>
@@ -87,8 +189,16 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -116,9 +226,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,31 +565,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C35B7D38-3B95-4814-ADF5-FDDC07DC885D}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.265625" customWidth="1"/>
     <col min="2" max="2" width="21.59765625" customWidth="1"/>
+    <col min="5" max="5" width="22.06640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.06640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -490,11 +621,26 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="1">
         <v>4000</v>
       </c>
+      <c r="H2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0.6</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -507,11 +653,26 @@
       <c r="D3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="1">
+      <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="1">
         <v>10000</v>
       </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" s="1">
+        <v>7000</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.2</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -524,11 +685,219 @@
       <c r="D4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1">
         <v>30000</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="1">
+        <v>12000</v>
+      </c>
+      <c r="J4" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5">
+        <v>45</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="1">
+        <v>50000</v>
+      </c>
+      <c r="H5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I5" s="1">
+        <v>20000</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="1">
+        <v>4000</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" s="1">
+        <v>20000</v>
+      </c>
+      <c r="H7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="1">
+        <v>8000</v>
+      </c>
+      <c r="J7" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="1">
+        <v>22000</v>
+      </c>
+      <c r="H8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I8" s="1">
+        <v>8400</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G9" s="1">
+        <v>12000</v>
+      </c>
+      <c r="H9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" s="1">
+        <v>11000</v>
+      </c>
+      <c r="H10" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>0.3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/examples/sales.xlsx
+++ b/examples/sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teoch\Documents\Personal\Github\approx\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A8BAAF-695B-4412-B994-3B3A014A6D00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3039E4-963D-4E5C-936C-3757E2EF50A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{FC993B36-9E35-4FE9-803B-9F990ACAC480}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="50">
   <si>
     <t>NRIC</t>
   </si>
@@ -180,6 +180,15 @@
   </si>
   <si>
     <t>2 Orchard Rd</t>
+  </si>
+  <si>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>This is a test, very long text, goes on forever. This is not sensitive but it shall pretend to be. Can the app detect it? It keeps going on and on. No identifiable information here, maybe? But perhaps… who knows?</t>
+  </si>
+  <si>
+    <t>GG</t>
   </si>
 </sst>
 </file>
@@ -565,7 +574,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C35B7D38-3B95-4814-ADF5-FDDC07DC885D}">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="13.265625" customWidth="1"/>
@@ -576,7 +585,7 @@
     <col min="10" max="10" width="18.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -607,8 +616,11 @@
       <c r="J1" s="2" t="s">
         <v>31</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -639,8 +651,11 @@
       <c r="J2" s="3">
         <v>0.6</v>
       </c>
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -671,8 +686,11 @@
       <c r="J3" s="3">
         <v>0.2</v>
       </c>
+      <c r="K3" t="s">
+        <v>49</v>
+      </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -704,7 +722,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>22</v>
       </c>
@@ -736,7 +754,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>32</v>
       </c>
@@ -768,7 +786,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>33</v>
       </c>
@@ -800,7 +818,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -832,7 +850,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -864,7 +882,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>36</v>
       </c>

--- a/examples/sales.xlsx
+++ b/examples/sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teoch\Documents\Personal\Github\approx\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A3039E4-963D-4E5C-936C-3757E2EF50A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BF65BB-EA5B-49F5-9EAB-E8B3B8C6A6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{FC993B36-9E35-4FE9-803B-9F990ACAC480}"/>
   </bookViews>
@@ -134,9 +134,6 @@
     <t>Compensation</t>
   </si>
   <si>
-    <t>Promotion Percentage</t>
-  </si>
-  <si>
     <t>S0931239E</t>
   </si>
   <si>
@@ -188,7 +185,10 @@
     <t>This is a test, very long text, goes on forever. This is not sensitive but it shall pretend to be. Can the app detect it? It keeps going on and on. No identifiable information here, maybe? But perhaps… who knows?</t>
   </si>
   <si>
-    <t>GG</t>
+    <t>Another example remark</t>
+  </si>
+  <si>
+    <t>Date of birth</t>
   </si>
 </sst>
 </file>
@@ -239,7 +239,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -579,10 +579,10 @@
   <cols>
     <col min="1" max="1" width="13.265625" customWidth="1"/>
     <col min="2" max="2" width="21.59765625" customWidth="1"/>
-    <col min="5" max="5" width="22.06640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.06640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.06640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.06640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
@@ -596,28 +596,28 @@
         <v>6</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -630,29 +630,29 @@
       <c r="C2">
         <v>27</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3">
+        <v>36333</v>
+      </c>
+      <c r="E2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>4000</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>3000</v>
       </c>
-      <c r="J2" s="3">
-        <v>0.6</v>
-      </c>
       <c r="K2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
@@ -665,29 +665,29 @@
       <c r="C3">
         <v>26</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3">
+        <v>36656</v>
+      </c>
+      <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>10000</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>7000</v>
       </c>
-      <c r="J3" s="3">
-        <v>0.2</v>
-      </c>
       <c r="K3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
@@ -700,26 +700,26 @@
       <c r="C4">
         <v>66</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3">
+        <v>22167</v>
+      </c>
+      <c r="E4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>30000</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>12000</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0.05</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -732,186 +732,186 @@
       <c r="C5">
         <v>45</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3">
+        <v>29851</v>
+      </c>
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>24</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>50000</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>29</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>20000</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0.1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6">
         <v>24</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3">
+        <v>44718</v>
+      </c>
+      <c r="E6" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>42</v>
-      </c>
       <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>10000</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>4000</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0.1</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>35</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="3">
+        <v>33278</v>
+      </c>
+      <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="E7" t="s">
-        <v>43</v>
-      </c>
       <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>20000</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>8000</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0.2</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C8">
         <v>36</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="3">
+        <v>32880</v>
+      </c>
+      <c r="E8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" t="s">
-        <v>44</v>
-      </c>
       <c r="F8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>22000</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>26</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>8400</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0.2</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C9">
         <v>20</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3">
+        <v>38791</v>
+      </c>
+      <c r="E9" t="s">
         <v>10</v>
       </c>
-      <c r="E9" t="s">
-        <v>45</v>
-      </c>
       <c r="F9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>12000</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>5000</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0.25</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>19</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="3">
+        <v>39312</v>
+      </c>
+      <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="E10" t="s">
-        <v>46</v>
-      </c>
       <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>11000</v>
       </c>
-      <c r="H10" t="s">
+      <c r="I10" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>5000</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0.3</v>
       </c>
     </row>
   </sheetData>

--- a/examples/sales.xlsx
+++ b/examples/sales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\teoch\Documents\Personal\Github\approx\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BF65BB-EA5B-49F5-9EAB-E8B3B8C6A6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712531F3-526B-450D-9D8F-644CD16C0A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{FC993B36-9E35-4FE9-803B-9F990ACAC480}"/>
   </bookViews>
@@ -131,9 +131,6 @@
     <t>Sales Director</t>
   </si>
   <si>
-    <t>Compensation</t>
-  </si>
-  <si>
     <t>S0931239E</t>
   </si>
   <si>
@@ -188,7 +185,10 @@
     <t>Another example remark</t>
   </si>
   <si>
-    <t>Date of birth</t>
+    <t>Phone Number</t>
+  </si>
+  <si>
+    <t>Date Of Birth</t>
   </si>
 </sst>
 </file>
@@ -235,11 +235,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,8 +587,8 @@
     <col min="2" max="2" width="21.59765625" customWidth="1"/>
     <col min="4" max="4" width="10.46484375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.06640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.06640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="14.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
@@ -604,20 +610,20 @@
       <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.45">
@@ -639,20 +645,20 @@
       <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="5">
+        <v>93386517</v>
+      </c>
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>4000</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="1">
-        <v>3000</v>
-      </c>
       <c r="K2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.45">
@@ -674,20 +680,20 @@
       <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="5">
+        <v>95552931</v>
+      </c>
+      <c r="H3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>10000</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="1">
-        <v>7000</v>
-      </c>
       <c r="K3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.45">
@@ -709,17 +715,17 @@
       <c r="F4" t="s">
         <v>16</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="5">
+        <v>85550533</v>
+      </c>
+      <c r="H4" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>30000</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>28</v>
-      </c>
-      <c r="J4" s="1">
-        <v>12000</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.45">
@@ -741,25 +747,25 @@
       <c r="F5" t="s">
         <v>24</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="5">
+        <v>95555298</v>
+      </c>
+      <c r="H5" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>50000</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>29</v>
-      </c>
-      <c r="J5" s="1">
-        <v>20000</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6">
         <v>24</v>
@@ -771,27 +777,27 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="5">
+        <v>88233412</v>
+      </c>
+      <c r="H6" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>10000</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>27</v>
-      </c>
-      <c r="J6" s="1">
-        <v>4000</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7">
         <v>35</v>
@@ -803,27 +809,27 @@
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="5">
+        <v>96464785</v>
+      </c>
+      <c r="H7" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>20000</v>
       </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
         <v>26</v>
-      </c>
-      <c r="J7" s="1">
-        <v>8000</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8">
         <v>36</v>
@@ -835,27 +841,27 @@
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="5">
+        <v>96332761</v>
+      </c>
+      <c r="H8" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>22000</v>
       </c>
-      <c r="I8" t="s">
+      <c r="J8" t="s">
         <v>26</v>
-      </c>
-      <c r="J8" s="1">
-        <v>8400</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -867,27 +873,27 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="5">
+        <v>97992060</v>
+      </c>
+      <c r="H9" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>12000</v>
       </c>
-      <c r="I9" t="s">
+      <c r="J9" t="s">
         <v>27</v>
-      </c>
-      <c r="J9" s="1">
-        <v>5000</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>19</v>
@@ -899,19 +905,19 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="5">
+        <v>93413004</v>
+      </c>
+      <c r="H10" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>11000</v>
       </c>
-      <c r="I10" t="s">
+      <c r="J10" t="s">
         <v>27</v>
-      </c>
-      <c r="J10" s="1">
-        <v>5000</v>
       </c>
     </row>
   </sheetData>
